--- a/public/templates/BLKPAY_TEMPLATE.xlsx
+++ b/public/templates/BLKPAY_TEMPLATE.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
@@ -14,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Beneficiary Name</t>
   </si>
@@ -133,30 +130,12 @@
 Note: Header label is editable in Row 1
 OPTIONAL</t>
   </si>
-  <si>
-    <t>IDFB0042841</t>
-  </si>
-  <si>
-    <t>NEFT</t>
-  </si>
-  <si>
-    <t>10078958844</t>
-  </si>
-  <si>
-    <t>INR</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Salary Jan 2026</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -177,25 +156,6 @@
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial Narrow"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial Narrow"/>
-    </font>
-    <font>
-      <color theme="10"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -261,19 +221,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -285,55 +239,11 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -363,44 +273,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -428,31 +338,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -480,23 +373,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -508,149 +384,208 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.85546875" style="1" customWidth="1"/>
@@ -662,242 +597,104 @@
     <col min="8" max="8" width="14.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="28" style="1" customWidth="1"/>
     <col min="10" max="15" width="23.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25" customHeight="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="38.25" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="102" customHeight="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" ht="102" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-    </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="14"/>
-    </row>
-    <row r="31" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="14"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="19"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1" insertColumns="0" insertRows="0" algorithmName="SHA-512" hashValue="sEzG1ltTB2yUh6I7WqbqDgCbu7sMUvUHvrzqu6u4oXNVCGPDo9IN8mxw+7phO9H9rW5Ik5nnnXaHUEnclaIUuA==" saltValue="s2pMyeq+9s0DaPR6fu8jyw==" spinCount="100000"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>